--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_275_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_275_R28.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.211</v>
+        <v>3.0354</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9982</v>
+        <v>1.0349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2128</v>
+        <v>2.0004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9392</v>
+        <v>-0.1707</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9928</v>
+        <v>0.3913</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0535</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3612</v>
+        <v>1.0553</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3612</v>
+        <v>0.9817</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.0736</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.422</v>
+        <v>-1.226</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3684</v>
+        <v>-0.5904</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0535</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2718</v>
+        <v>0.7422</v>
       </c>
       <c r="T2" t="n">
-        <v>0.637</v>
+        <v>0.0672</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6348</v>
+        <v>0.675</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9339</v>
+        <v>1.8071</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1081</v>
+        <v>1.7623</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1742</v>
+        <v>0.0448</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1596</v>
+        <v>0.9392</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5677</v>
+        <v>0.9928</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4081</v>
+        <v>-0.0535</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3748</v>
+        <v>1.3612</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4618</v>
+        <v>1.3612</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0871</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2152</v>
+        <v>-0.422</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8942</v>
+        <v>-0.3684</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3211</v>
+        <v>-0.0535</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8619</v>
+        <v>0.8678</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6765</v>
+        <v>0.4011</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1854</v>
+        <v>0.4668</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6673</v>
+        <v>1.4278</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3486</v>
+        <v>2.4004</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3186</v>
+        <v>-0.9726</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.7258</v>
+        <v>2.1596</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3865</v>
+        <v>2.5677</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.3393</v>
+        <v>-0.4081</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3961</v>
+        <v>3.3748</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6757</v>
+        <v>3.4618</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.0718</v>
+        <v>-0.0871</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3298</v>
+        <v>-1.2152</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0622</v>
+        <v>-0.8942</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2676</v>
+        <v>-0.3211</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8417</v>
+        <v>0.3558</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7447</v>
+        <v>-0.0312</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0969</v>
+        <v>0.387</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3368</v>
+        <v>0.0641</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.294</v>
+        <v>1.0172</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6308</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1707</v>
+        <v>-0.4894</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3913</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.2944</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0553</v>
+        <v>1.5517</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9817</v>
+        <v>0.5714</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.226</v>
+        <v>-2.041</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5904</v>
+        <v>-1.3552</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.6859</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9564</v>
+        <v>-0.3743</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2617</v>
+        <v>-0.3025</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3053</v>
+        <v>-0.0718</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.182</v>
+        <v>-0.0267</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0973</v>
+        <v>-1.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2793</v>
+        <v>1.0834</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9675</v>
+        <v>-3.7258</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2908</v>
+        <v>-0.3865</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6767</v>
+        <v>-3.3393</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0941</v>
+        <v>-2.3961</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5818</v>
+        <v>0.6757</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-3.0718</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8734</v>
+        <v>-1.3298</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8726</v>
+        <v>-1.0622</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0008</v>
+        <v>-0.2676</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.0154</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>2.598</v>
+        <v>2.1477</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2467</v>
+        <v>1.286</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3513</v>
+        <v>0.8617</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0813</v>
+        <v>-0.537</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1352</v>
+        <v>-0.2242</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0539</v>
+        <v>-0.3129</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4894</v>
+        <v>0.3711</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-0.5558</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2944</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5517</v>
+        <v>-0.1614</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5714</v>
+        <v>-0.1982</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.041</v>
+        <v>0.5324</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3552</v>
+        <v>-0.3577</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6859</v>
+        <v>0.8901</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3572</v>
+        <v>-0.2998</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1726</v>
+        <v>-0.237</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7393</v>
+        <v>-0.9141</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4601</v>
+        <v>-0.6556</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2792</v>
+        <v>-0.2584</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3711</v>
+        <v>-2.9675</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5558</v>
+        <v>-0.2908</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9268999999999999</v>
+        <v>-2.6767</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1614</v>
+        <v>-0.0941</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1982</v>
+        <v>0.5818</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5324</v>
+        <v>-2.8734</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3577</v>
+        <v>-0.8726</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8901</v>
+        <v>-2.0008</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>3.0154</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5021</v>
+        <v>1.502</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2987</v>
+        <v>0.6884</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2034</v>
+        <v>0.8136</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.075</v>
+        <v>-1.4119</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5788</v>
+        <v>-1.8469</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5038</v>
+        <v>0.435</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0386</v>
+        <v>-3.4084</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5702</v>
+        <v>0.1151</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4684</v>
+        <v>-3.5235</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0773</v>
+        <v>-1.196</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7191</v>
+        <v>1.1665</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3581</v>
+        <v>-2.3626</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9613</v>
+        <v>-2.2123</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.851</v>
+        <v>-1.0514</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1103</v>
+        <v>-1.1609</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0365</v>
+        <v>0.6743</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1098</v>
+        <v>0.2047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.4696</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6319</v>
+        <v>-2.2026</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8652</v>
+        <v>-2.74</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2333</v>
+        <v>0.5374</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4084</v>
+        <v>-2.0386</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1151</v>
+        <v>-1.5702</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.5235</v>
+        <v>-0.4684</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.196</v>
+        <v>-1.0773</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1665</v>
+        <v>-0.7191</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3626</v>
+        <v>-0.3581</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2123</v>
+        <v>-0.9613</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0514</v>
+        <v>-0.851</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1609</v>
+        <v>-0.1103</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5456</v>
+        <v>-0.1641</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8136</v>
+        <v>-0.2711</v>
       </c>
       <c r="U10" t="n">
-        <v>0.268</v>
+        <v>0.107</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9733</v>
+        <v>-4.47</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9388</v>
+        <v>-5.4356</v>
       </c>
       <c r="F11" t="n">
         <v>0.9656</v>
@@ -1312,10 +1312,10 @@
         <v>2.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7275</v>
+        <v>1.2307</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2363</v>
+        <v>0.7395</v>
       </c>
       <c r="U11" t="n">
         <v>0.4911</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1365</v>
+        <v>-6.169</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1822</v>
+        <v>-5.2818</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9543</v>
+        <v>-0.8871</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6967</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1204</v>
+        <v>0.8472</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7468</v>
+        <v>0.1535</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6264</v>
+        <v>0.6937</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.1437</v>
+        <v>-9.396899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.8263</v>
+        <v>-11.0793</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6826</v>
+        <v>1.682499999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-19.5296</v>
@@ -1456,7 +1456,7 @@
         <v>-8.887600000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.3022</v>
+        <v>-5.302199999999999</v>
       </c>
       <c r="P13" t="n">
         <v>2.3195</v>
@@ -1468,22 +1468,22 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>6.782699999999999</v>
+        <v>7.529499999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1261</v>
+        <v>2.8728</v>
       </c>
       <c r="U13" t="n">
-        <v>4.656600000000001</v>
+        <v>4.6567</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2835</v>
+        <v>0.2835000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>6.464200000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.1807</v>
+        <v>-6.180700000000002</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3436</v>
+        <v>6.899</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7174</v>
+        <v>4.0712</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6262</v>
+        <v>2.8278</v>
       </c>
       <c r="G14" t="n">
         <v>6.3563</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.281</v>
+        <v>-0.7255</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8215</v>
+        <v>-0.4676</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4595</v>
+        <v>-0.2579</v>
       </c>
       <c r="V14" t="n">
         <v>2.428</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7069</v>
+        <v>4.0665</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1159</v>
+        <v>3.3518</v>
       </c>
       <c r="F15" t="n">
-        <v>0.591</v>
+        <v>0.7147</v>
       </c>
       <c r="G15" t="n">
         <v>2.8973</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0486</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>-0.727</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0857</v>
+        <v>0.038</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2122</v>
+        <v>1.9256</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3155</v>
+        <v>0.9617</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.9639</v>
       </c>
       <c r="G16" t="n">
         <v>3.1832</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.203</v>
+        <v>-0.4896</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1889</v>
+        <v>-0.165</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3918</v>
+        <v>-0.3246</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.544</v>
+        <v>1.667</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4171</v>
+        <v>-2.653</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9612</v>
+        <v>4.3201</v>
       </c>
       <c r="G17" t="n">
         <v>3.9693</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4279</v>
+        <v>-0.3049</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2592</v>
+        <v>-0.4951</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1687</v>
+        <v>0.1902</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.0591</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5212</v>
+        <v>-1.4032</v>
       </c>
       <c r="F18" t="n">
-        <v>2.059</v>
+        <v>2.4623</v>
       </c>
       <c r="G18" t="n">
         <v>0.9727</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3627</v>
+        <v>-0.8415</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>-0.7035</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5412</v>
+        <v>-0.1379</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0538</v>
+        <v>0.497</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8986</v>
+        <v>2.0165</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8448</v>
+        <v>-1.5195</v>
       </c>
       <c r="G19" t="n">
         <v>5.421</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5116</v>
+        <v>-1.0684</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8136</v>
+        <v>-0.6956</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.698</v>
+        <v>-0.3727</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.102</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0269</v>
+        <v>0.6654</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9414</v>
+        <v>-0.7674</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5043</v>
+        <v>1.0101</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5473</v>
+        <v>-0.7933</v>
       </c>
       <c r="I20" t="n">
-        <v>3.0517</v>
+        <v>1.8034</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7469</v>
+        <v>2.2221</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9677</v>
+        <v>0.1008</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2208</v>
+        <v>2.1212</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2512</v>
+        <v>-1.212</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5796</v>
+        <v>-0.8942</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8308</v>
+        <v>-0.3178</v>
       </c>
       <c r="P20" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1782</v>
+        <v>-1.0605</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0395</v>
+        <v>-0.3969</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1387</v>
+        <v>-0.6636</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.388</v>
+        <v>-0.8528</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5475</v>
+        <v>-2.5798</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9354</v>
+        <v>1.727</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0101</v>
+        <v>-1.6646</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7933</v>
+        <v>-0.3228</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8034</v>
+        <v>-1.3418</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2221</v>
+        <v>-2.2182</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1008</v>
+        <v>0.0672</v>
       </c>
       <c r="L21" t="n">
-        <v>2.1212</v>
+        <v>-2.2854</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.212</v>
+        <v>0.5536</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8942</v>
+        <v>-0.39</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3178</v>
+        <v>0.9436</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3465</v>
+        <v>-0.5799</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5149</v>
+        <v>-0.3615</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8316</v>
+        <v>-0.2183</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4529</v>
+        <v>-0.9734</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9113</v>
+        <v>-0.7933</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4584</v>
+        <v>-0.1801</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2859</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.2249</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1857</v>
+        <v>0.5472</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4476</v>
+        <v>-1.1558</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8157</v>
+        <v>-3.3807</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3681</v>
+        <v>2.2249</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6646</v>
+        <v>1.5043</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3228</v>
+        <v>-1.5473</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3418</v>
+        <v>3.0517</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.2182</v>
+        <v>-0.7469</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0672</v>
+        <v>-0.9677</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2854</v>
+        <v>0.2208</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5536</v>
+        <v>2.2512</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.39</v>
+        <v>-0.5796</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9436</v>
+        <v>2.8308</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1747</v>
+        <v>0.1079</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.3143</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5772</v>
+        <v>0.4222</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8807</v>
+        <v>-2.1002</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0492</v>
+        <v>-1.4031</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8315</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8343</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3506</v>
+        <v>-0.57</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3462</v>
+        <v>-0.0077</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6967</v>
+        <v>-0.5623</v>
       </c>
       <c r="V24" t="n">
         <v>1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.1436</v>
+        <v>10.93</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.146500000000001</v>
+        <v>-1.1465</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2903</v>
+        <v>12.0766</v>
       </c>
       <c r="G25" t="n">
         <v>19.5294</v>
@@ -2380,7 +2380,7 @@
         <v>14.1897</v>
       </c>
       <c r="K25" t="n">
-        <v>8.887600000000001</v>
+        <v>8.887599999999999</v>
       </c>
       <c r="L25" t="n">
         <v>5.302099999999999</v>
@@ -2404,13 +2404,13 @@
         <v>15.077</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.7829</v>
+        <v>-5.9965</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.6568</v>
+        <v>-4.6564</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.126</v>
+        <v>-1.3397</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2836000000000003</v>
@@ -2419,7 +2419,7 @@
         <v>6.716800000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.000400000000001</v>
+        <v>-7.000399999999999</v>
       </c>
     </row>
   </sheetData>
